--- a/resources/office-templates/01-bar-daily-cases.xlsx
+++ b/resources/office-templates/01-bar-daily-cases.xlsx
@@ -667,7 +667,10 @@
       <c r="C2" s="4" t="n">
         <v>1402</v>
       </c>
-      <c r="D2" s="4" t="inlineStr"/>
+      <c r="D2" s="4">
+        <f>AVERAGE(C2:C2)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -683,7 +686,10 @@
       <c r="C3" s="4" t="n">
         <v>1108</v>
       </c>
-      <c r="D3" s="4" t="inlineStr"/>
+      <c r="D3" s="4">
+        <f>AVERAGE(C2:C3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -699,7 +705,10 @@
       <c r="C4" s="4" t="n">
         <v>1090</v>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="D4" s="4">
+        <f>AVERAGE(C2:C4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -716,7 +725,7 @@
         <v>1706</v>
       </c>
       <c r="D5" s="4">
-        <f>AVERAGE(C2:C8)</f>
+        <f>AVERAGE(C2:C5)</f>
         <v/>
       </c>
     </row>
@@ -735,7 +744,7 @@
         <v>1771</v>
       </c>
       <c r="D6" s="4">
-        <f>AVERAGE(C3:C9)</f>
+        <f>AVERAGE(C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -754,7 +763,7 @@
         <v>1988</v>
       </c>
       <c r="D7" s="4">
-        <f>AVERAGE(C4:C10)</f>
+        <f>AVERAGE(C2:C7)</f>
         <v/>
       </c>
     </row>
@@ -773,7 +782,7 @@
         <v>1920</v>
       </c>
       <c r="D8" s="4">
-        <f>AVERAGE(C5:C11)</f>
+        <f>AVERAGE(C2:C8)</f>
         <v/>
       </c>
     </row>
@@ -792,7 +801,7 @@
         <v>2102</v>
       </c>
       <c r="D9" s="4">
-        <f>AVERAGE(C6:C12)</f>
+        <f>AVERAGE(C3:C9)</f>
         <v/>
       </c>
     </row>
@@ -811,7 +820,7 @@
         <v>1301</v>
       </c>
       <c r="D10" s="4">
-        <f>AVERAGE(C7:C13)</f>
+        <f>AVERAGE(C4:C10)</f>
         <v/>
       </c>
     </row>
@@ -830,7 +839,7 @@
         <v>1454</v>
       </c>
       <c r="D11" s="4">
-        <f>AVERAGE(C8:C14)</f>
+        <f>AVERAGE(C5:C11)</f>
         <v/>
       </c>
     </row>
@@ -849,7 +858,7 @@
         <v>2630</v>
       </c>
       <c r="D12" s="4">
-        <f>AVERAGE(C9:C15)</f>
+        <f>AVERAGE(C6:C12)</f>
         <v/>
       </c>
     </row>
@@ -868,7 +877,7 @@
         <v>2487</v>
       </c>
       <c r="D13" s="4">
-        <f>AVERAGE(C10:C16)</f>
+        <f>AVERAGE(C7:C13)</f>
         <v/>
       </c>
     </row>
@@ -887,7 +896,7 @@
         <v>2872</v>
       </c>
       <c r="D14" s="4">
-        <f>AVERAGE(C11:C17)</f>
+        <f>AVERAGE(C8:C14)</f>
         <v/>
       </c>
     </row>
@@ -906,7 +915,7 @@
         <v>2699</v>
       </c>
       <c r="D15" s="4">
-        <f>AVERAGE(C12:C18)</f>
+        <f>AVERAGE(C9:C15)</f>
         <v/>
       </c>
     </row>
@@ -925,7 +934,7 @@
         <v>3059</v>
       </c>
       <c r="D16" s="4">
-        <f>AVERAGE(C13:C19)</f>
+        <f>AVERAGE(C10:C16)</f>
         <v/>
       </c>
     </row>
@@ -944,7 +953,7 @@
         <v>1751</v>
       </c>
       <c r="D17" s="4">
-        <f>AVERAGE(C14:C20)</f>
+        <f>AVERAGE(C11:C17)</f>
         <v/>
       </c>
     </row>
@@ -963,7 +972,7 @@
         <v>1790</v>
       </c>
       <c r="D18" s="4">
-        <f>AVERAGE(C15:C21)</f>
+        <f>AVERAGE(C12:C18)</f>
         <v/>
       </c>
     </row>
@@ -982,7 +991,7 @@
         <v>3149</v>
       </c>
       <c r="D19" s="4">
-        <f>AVERAGE(C16:C22)</f>
+        <f>AVERAGE(C13:C19)</f>
         <v/>
       </c>
     </row>
@@ -1001,7 +1010,7 @@
         <v>3408</v>
       </c>
       <c r="D20" s="4">
-        <f>AVERAGE(C17:C23)</f>
+        <f>AVERAGE(C14:C20)</f>
         <v/>
       </c>
     </row>
@@ -1020,7 +1029,7 @@
         <v>3457</v>
       </c>
       <c r="D21" s="4">
-        <f>AVERAGE(C18:C24)</f>
+        <f>AVERAGE(C15:C21)</f>
         <v/>
       </c>
     </row>
@@ -1039,7 +1048,7 @@
         <v>3643</v>
       </c>
       <c r="D22" s="4">
-        <f>AVERAGE(C19:C25)</f>
+        <f>AVERAGE(C16:C22)</f>
         <v/>
       </c>
     </row>
@@ -1058,7 +1067,7 @@
         <v>3693</v>
       </c>
       <c r="D23" s="4">
-        <f>AVERAGE(C20:C26)</f>
+        <f>AVERAGE(C17:C23)</f>
         <v/>
       </c>
     </row>
@@ -1077,7 +1086,7 @@
         <v>2405</v>
       </c>
       <c r="D24" s="4">
-        <f>AVERAGE(C21:C27)</f>
+        <f>AVERAGE(C18:C24)</f>
         <v/>
       </c>
     </row>
@@ -1096,7 +1105,7 @@
         <v>2271</v>
       </c>
       <c r="D25" s="4">
-        <f>AVERAGE(C22:C28)</f>
+        <f>AVERAGE(C19:C25)</f>
         <v/>
       </c>
     </row>
@@ -1115,7 +1124,7 @@
         <v>3976</v>
       </c>
       <c r="D26" s="4">
-        <f>AVERAGE(C23:C29)</f>
+        <f>AVERAGE(C20:C26)</f>
         <v/>
       </c>
     </row>
@@ -1133,7 +1142,10 @@
       <c r="C27" s="4" t="n">
         <v>3960</v>
       </c>
-      <c r="D27" s="4" t="inlineStr"/>
+      <c r="D27" s="4">
+        <f>AVERAGE(C21:C27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1149,7 +1161,10 @@
       <c r="C28" s="4" t="n">
         <v>4213</v>
       </c>
-      <c r="D28" s="4" t="inlineStr"/>
+      <c r="D28" s="4">
+        <f>AVERAGE(C22:C28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1165,7 +1180,10 @@
       <c r="C29" s="4" t="n">
         <v>4021</v>
       </c>
-      <c r="D29" s="4" t="inlineStr"/>
+      <c r="D29" s="4">
+        <f>AVERAGE(C23:C29)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1194,14 +1212,14 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Pattern A:主色 + 7 日中心對齊移動平均</t>
+          <t>Pattern A:主色 + 7 日 trailing 移動平均(本日含前 6 日)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>色彩:#739A6D 直條 + #374C34 均線。Y 軸從零開始;不截斷座標。</t>
+          <t>色彩:#739A6D 直條 + #374C34 均線。Y 軸從零開始;不截斷座標。前 6 天用自適應累積窗口。</t>
         </is>
       </c>
     </row>
